--- a/deploy/133_ENT_OFF_CONVAL/75 OFF_CONVAL.xlsx
+++ b/deploy/133_ENT_OFF_CONVAL/75 OFF_CONVAL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LOCAL\DESA\non-purple-wheel\non-purple-wheel\deploy\133_ENT_OFF_CONVAL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A42491C-3006-4B08-9F34-C9293F76A9A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F49EA1B4-7396-4C8C-AF45-380EA107EB84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9420" yWindow="1340" windowWidth="21830" windowHeight="13000" xr2:uid="{30C1FAAF-C51A-4EA9-BA91-28A12E2383B8}"/>
+    <workbookView xWindow="13120" yWindow="6140" windowWidth="21830" windowHeight="13000" xr2:uid="{30C1FAAF-C51A-4EA9-BA91-28A12E2383B8}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="76">
   <si>
     <t>FE_CON_OPE</t>
   </si>
@@ -222,6 +222,51 @@
   </si>
   <si>
     <t>GAR-OFF133-010</t>
+  </si>
+  <si>
+    <t>OFF133-0000000011</t>
+  </si>
+  <si>
+    <t>PAQ-OFF133-011</t>
+  </si>
+  <si>
+    <t>GAR-OFF133-011</t>
+  </si>
+  <si>
+    <t>OFF133-0000000012</t>
+  </si>
+  <si>
+    <t>PAQ-OFF133-012</t>
+  </si>
+  <si>
+    <t>GAR-OFF133-012</t>
+  </si>
+  <si>
+    <t>OFF133-0000000013</t>
+  </si>
+  <si>
+    <t>PAQ-OFF133-013</t>
+  </si>
+  <si>
+    <t>GAR-OFF133-013</t>
+  </si>
+  <si>
+    <t>OFF133-0000000014</t>
+  </si>
+  <si>
+    <t>PAQ-OFF133-014</t>
+  </si>
+  <si>
+    <t>GAR-OFF133-014</t>
+  </si>
+  <si>
+    <t>OFF133-0000000015</t>
+  </si>
+  <si>
+    <t>PAQ-OFF133-015</t>
+  </si>
+  <si>
+    <t>GAR-OFF133-015</t>
   </si>
 </sst>
 </file>
@@ -594,7 +639,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C2C369C-EF5E-45EF-8B02-62C5DCBFC05C}">
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="17.90625" bestFit="1" customWidth="1"/>
@@ -979,7 +1024,7 @@
         <v>48</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="D8" t="s">
         <v>49</v>
@@ -1032,7 +1077,7 @@
         <v>52</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s">
         <v>19</v>
@@ -1138,7 +1183,7 @@
         <v>58</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s">
         <v>30</v>
@@ -1181,6 +1226,271 @@
       </c>
       <c r="Q11" s="1">
         <v>46192</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A12" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12">
+        <v>7</v>
+      </c>
+      <c r="F12" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12">
+        <v>75</v>
+      </c>
+      <c r="H12">
+        <v>800000</v>
+      </c>
+      <c r="I12" t="s">
+        <v>21</v>
+      </c>
+      <c r="J12">
+        <v>790000</v>
+      </c>
+      <c r="K12" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12">
+        <v>90</v>
+      </c>
+      <c r="M12">
+        <v>90</v>
+      </c>
+      <c r="N12" t="s">
+        <v>63</v>
+      </c>
+      <c r="O12">
+        <v>2800000</v>
+      </c>
+      <c r="P12" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A13" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13">
+        <v>7</v>
+      </c>
+      <c r="F13" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13">
+        <v>420</v>
+      </c>
+      <c r="H13">
+        <v>5000000</v>
+      </c>
+      <c r="I13" t="s">
+        <v>21</v>
+      </c>
+      <c r="J13">
+        <v>4950000</v>
+      </c>
+      <c r="K13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13">
+        <v>450</v>
+      </c>
+      <c r="M13">
+        <v>450</v>
+      </c>
+      <c r="N13" t="s">
+        <v>66</v>
+      </c>
+      <c r="O13">
+        <v>16000000</v>
+      </c>
+      <c r="P13" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A14" s="1">
+        <v>46193</v>
+      </c>
+      <c r="B14" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14">
+        <v>7</v>
+      </c>
+      <c r="F14" t="s">
+        <v>68</v>
+      </c>
+      <c r="G14">
+        <v>180</v>
+      </c>
+      <c r="H14">
+        <v>2200000</v>
+      </c>
+      <c r="I14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J14">
+        <v>2180000</v>
+      </c>
+      <c r="K14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14">
+        <v>180</v>
+      </c>
+      <c r="M14">
+        <v>180</v>
+      </c>
+      <c r="N14" t="s">
+        <v>69</v>
+      </c>
+      <c r="O14">
+        <v>7000000</v>
+      </c>
+      <c r="P14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>46193</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A15" s="1">
+        <v>46193</v>
+      </c>
+      <c r="B15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15">
+        <v>7</v>
+      </c>
+      <c r="F15" t="s">
+        <v>71</v>
+      </c>
+      <c r="G15">
+        <v>270</v>
+      </c>
+      <c r="H15">
+        <v>3800000</v>
+      </c>
+      <c r="I15" t="s">
+        <v>21</v>
+      </c>
+      <c r="J15">
+        <v>3760000</v>
+      </c>
+      <c r="K15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15">
+        <v>270</v>
+      </c>
+      <c r="M15">
+        <v>270</v>
+      </c>
+      <c r="N15" t="s">
+        <v>72</v>
+      </c>
+      <c r="O15">
+        <v>13000000</v>
+      </c>
+      <c r="P15" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>46193</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A16" s="1">
+        <v>46193</v>
+      </c>
+      <c r="B16" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16">
+        <v>7</v>
+      </c>
+      <c r="F16" t="s">
+        <v>74</v>
+      </c>
+      <c r="G16">
+        <v>600</v>
+      </c>
+      <c r="H16">
+        <v>9000000</v>
+      </c>
+      <c r="I16" t="s">
+        <v>21</v>
+      </c>
+      <c r="J16">
+        <v>8900000</v>
+      </c>
+      <c r="K16" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16">
+        <v>730</v>
+      </c>
+      <c r="M16">
+        <v>730</v>
+      </c>
+      <c r="N16" t="s">
+        <v>75</v>
+      </c>
+      <c r="O16">
+        <v>30000000</v>
+      </c>
+      <c r="P16" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>46193</v>
       </c>
     </row>
   </sheetData>
